--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/processDelegate.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/processDelegate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>委托编号</t>
   </si>
@@ -1011,8 +1011,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I115"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="19.875" customWidth="1"/>
@@ -1025,66 +1025,61 @@
     <col min="9" max="9" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="114" spans="1:9">
-      <c r="A114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1</v>
-      </c>
-      <c r="C114" t="s">
-        <v>2</v>
-      </c>
-      <c r="D114" t="s">
-        <v>3</v>
-      </c>
-      <c r="E114" t="s">
-        <v>4</v>
-      </c>
-      <c r="F114" t="s">
-        <v>5</v>
-      </c>
-      <c r="G114" t="s">
-        <v>6</v>
-      </c>
-      <c r="H114" t="s">
-        <v>7</v>
-      </c>
-      <c r="I114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
-      <c r="A115" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I115" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
     </row>
